--- a/Remaining_Clashes_v2.5.xlsx
+++ b/Remaining_Clashes_v2.5.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Remaining Clashes'!$A$1:$L$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Remaining Clashes'!$A$1:$L$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -552,12 +552,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>106261</t>
+          <t>106275</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Aviles, Zavier</t>
+          <t>LaBarbiera, Thomas</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -588,7 +588,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -603,19 +603,19 @@
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>450 Calculus H</t>
+          <t>732 Business Law</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>106258</t>
+          <t>106271</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>McCarthy, Blake</t>
+          <t>Hannon, Ethan</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
@@ -646,7 +646,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -661,19 +661,19 @@
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>450 Calculus H</t>
+          <t>849 Catholic Social Teaching</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>111831</t>
+          <t>106299</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Foster, Alexander</t>
+          <t>Geraci, Joseph</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -704,7 +704,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -719,40 +719,40 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>851 Spirituality of Vocation</t>
+          <t>727 Sports and Entertainment Marketing</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>107004</t>
+          <t>106258</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Patterson, Colin</t>
+          <t>McCarthy, Blake</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>543</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>CPR-AED Training/PE</t>
+          <t>Anatomy/Physiology H</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>flexible</t>
+          <t>limited_choice</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -767,7 +767,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Full-Year</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -777,40 +777,40 @@
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>830 Theology 11</t>
+          <t>595 Engineering Design</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>116815</t>
+          <t>106197</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>DellaVolpe, Louis</t>
+          <t>Gornell, Finbar</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>543</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>CPR-AED Training/PE</t>
+          <t>Anatomy/Physiology H</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>flexible</t>
+          <t>limited_choice</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Full-Year</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -835,19 +835,19 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>432 Algebra II/Trig</t>
+          <t>851 Spirituality of Vocation</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>111947</t>
+          <t>107889</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Arias Parra, Eliezer</t>
+          <t>Petrosino, Nicholas</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
@@ -878,7 +878,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -893,19 +893,19 @@
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>130 British Literature</t>
+          <t>131 British Literature H</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>109580</t>
+          <t>106791</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Drossos, Vasilios</t>
+          <t>Guirland, Gavin</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -951,19 +951,19 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>339 Latin III H</t>
+          <t>530 Physics</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>108402</t>
+          <t>119514</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Hutmacher, Terence</t>
+          <t>Roemer, Thomas</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
@@ -994,12 +994,12 @@
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -1009,19 +1009,19 @@
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>730 U.S. History II</t>
+          <t>741 Psychology</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>107653</t>
+          <t>110133</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Negron, Michael</t>
+          <t>Ruiz, Kyle</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -1052,12 +1052,12 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
@@ -1067,19 +1067,19 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>330 Spanish III</t>
+          <t>830 Theology 11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>107048</t>
+          <t>109580</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>McAlear, Cole</t>
+          <t>Drossos, Vasilios</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1125,19 +1125,19 @@
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>830 Theology 11</t>
+          <t>530 Physics</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>121384</t>
+          <t>108402</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Ryzy, Martin</t>
+          <t>Hutmacher, Terence</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
@@ -1183,32 +1183,32 @@
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>440 Precalculus</t>
+          <t>830 Theology 11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>117132</t>
+          <t>108111</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Jean-Marie, Samuel</t>
+          <t>George, Jacob</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>631</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Fitness/PE</t>
+          <t>CPR-AED Training/PE</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1241,32 +1241,32 @@
       </c>
       <c r="L13" s="5" t="inlineStr">
         <is>
-          <t>440 Precalculus</t>
+          <t>531 Physics H</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>106308</t>
+          <t>107653</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Chiusano, Dean</t>
+          <t>Negron, Michael</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>631</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Fitness/PE</t>
+          <t>CPR-AED Training/PE</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
@@ -1299,32 +1299,32 @@
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>851 Spirituality of Vocation</t>
+          <t>530 Physics</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>106257</t>
+          <t>107279</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Ekins, Aidan</t>
+          <t>Bruno, Jake</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>631</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Nutrition &amp; Fitness/PE</t>
+          <t>CPR-AED Training/PE</t>
         </is>
       </c>
       <c r="F15" s="4" t="n">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1357,32 +1357,32 @@
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>440 Precalculus</t>
+          <t>130 British Literature</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>113761</t>
+          <t>107048</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Davis, Isaiah</t>
+          <t>McAlear, Cole</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>631</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>Physics</t>
+          <t>CPR-AED Training/PE</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Full-Year</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -1415,36 +1415,36 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>143 Creative Writing</t>
+          <t>331 Spanish III H</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>121012</t>
+          <t>107904</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>121012</t>
+          <t>Uetani, Reo</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>631</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Robotics</t>
+          <t>CPR-AED Training/PE</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
@@ -1473,19 +1473,19 @@
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>610 Health/PE</t>
+          <t>585 Robotics Design</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>108163</t>
+          <t>121384</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Mathews, Noah</t>
+          <t>Ryzy, Martin</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
@@ -1493,16 +1493,16 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>631</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Business Law</t>
+          <t>CPR-AED Training/PE</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -1531,19 +1531,19 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>733 AP U.S. History</t>
+          <t>131 British Literature H</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>116815</t>
+          <t>108666</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>DellaVolpe, Louis</t>
+          <t>Foye, John</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
@@ -1551,16 +1551,16 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>631</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>TV/Film Production II</t>
+          <t>CPR-AED Training/PE</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="K19" s="5" t="inlineStr">
@@ -1589,36 +1589,36 @@
       </c>
       <c r="L19" s="5" t="inlineStr">
         <is>
-          <t>730 U.S. History II</t>
+          <t>339 Latin III H</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>109471</t>
+          <t>106313</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Shaikh, Adam</t>
+          <t>Phillips, Joaquin</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>642</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>International Business Strategies</t>
+          <t>Nutrition &amp; Fitness/PE</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Full-Year</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
@@ -1647,36 +1647,36 @@
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>139 AP English Language</t>
+          <t>955 Academic Support</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>106869</t>
+          <t>116044</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Hanabergh, Daniel</t>
+          <t>Brudney, Denzin</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>642</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Programming</t>
+          <t>Nutrition &amp; Fitness/PE</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1705,36 +1705,36 @@
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>830 Theology 11</t>
+          <t>851 Spirituality of Vocation</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>119514</t>
+          <t>106272</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Roemer, Thomas</t>
+          <t>Esparra, Tomas</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>642</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Sports and Entertainment Marketing</t>
+          <t>Nutrition &amp; Fitness/PE</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1763,36 +1763,36 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>830 Theology 11</t>
+          <t>752 Economics H</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>117105</t>
+          <t>106347</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Thomas, Ca'Si</t>
+          <t>Jackson, Terrence</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>642</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Sports and Entertainment Marketing</t>
+          <t>Nutrition &amp; Fitness/PE</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
@@ -1821,36 +1821,36 @@
       </c>
       <c r="L23" s="5" t="inlineStr">
         <is>
-          <t>430 Algebra II/Trig</t>
+          <t>851 Spirituality of Vocation</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>110396</t>
+          <t>106256</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Riccardi, Christian</t>
+          <t>Higgins, Viktor</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>642</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Business Law</t>
+          <t>Nutrition &amp; Fitness/PE</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1879,36 +1879,36 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>730 U.S. History II</t>
+          <t>744 Sociology</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>109824</t>
+          <t>113761</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Rankin, Henry</t>
+          <t>Davis, Isaiah</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>530</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>TV/Film Process and Principles</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Full-Year</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
@@ -1937,36 +1937,36 @@
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>430 Algebra II/Trig</t>
+          <t>143 Creative Writing</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>108828</t>
+          <t>111850</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Valente, Joseph</t>
+          <t>Dukes, Steven</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>530</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>TV/Film Production II</t>
+          <t>Physics</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Full-Year</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -1995,32 +1995,32 @@
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>631 CPR-AED Training/PE</t>
+          <t>851 Spirituality of Vocation</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>108622</t>
+          <t>121012</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Sasso, Daniel</t>
+          <t>121012</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>570</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Digital Media</t>
+          <t>Introduction to Robotics</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>139 AP English Language</t>
+          <t>310 Spanish I</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>108388</t>
+          <t>107004</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Desdunes, Olivier</t>
+          <t>Patterson, Colin</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
@@ -2111,19 +2111,19 @@
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>430 Algebra II/Trig</t>
+          <t>130 British Literature</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>108437</t>
+          <t>108163</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Basich, Tomislav</t>
+          <t>Mathews, Noah</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>732</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>TV/Film Production &amp; Editing I</t>
+          <t>Business Law</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
@@ -2154,34 +2154,34 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>singleton_collision</t>
+          <t>period_saturation</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>830 Theology 11</t>
+          <t>733 AP U.S. History</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>108070</t>
+          <t>108803</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Robins, Sean</t>
+          <t>Maciejewski, John</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2227,19 +2227,19 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>130 British Literature</t>
+          <t>530 Physics</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>108137</t>
+          <t>108608</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Egbert, Gabriel</t>
+          <t>Walsh, Joseph</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>TV/Film Production &amp; Editing I</t>
+          <t>Studio Art I</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
@@ -2275,29 +2275,29 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>singleton_collision</t>
+          <t>period_saturation</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>310 Spanish I</t>
+          <t>733 AP U.S. History</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>107150</t>
+          <t>119514</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Ferro, Preston</t>
+          <t>Roemer, Thomas</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>727</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Studio Art I</t>
+          <t>Sports and Entertainment Marketing</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -2343,19 +2343,19 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>830 Theology 11</t>
+          <t>741 Psychology</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>107177</t>
+          <t>117105</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Siracuse, David</t>
+          <t>Thomas, Ca'Si</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>727</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Programming</t>
+          <t>Sports and Entertainment Marketing</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
@@ -2401,19 +2401,19 @@
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>331 Spanish III H</t>
+          <t>430 Algebra II/Trig</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>119656</t>
+          <t>110396</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Pierce, Dylan</t>
+          <t>Riccardi, Christian</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>732</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>Sports and Entertainment Marketing</t>
+          <t>Business Law</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2459,19 +2459,19 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>330 Spanish III</t>
+          <t>727 Sports and Entertainment Marketing</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>110098</t>
+          <t>109824</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Arment, Jayden</t>
+          <t>Rankin, Henry</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Studio Art I</t>
+          <t>TV/Film Process and Principles</t>
         </is>
       </c>
       <c r="F35" s="4" t="n">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
@@ -2517,19 +2517,19 @@
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>830 Theology 11</t>
+          <t>430 Algebra II/Trig</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>108061</t>
+          <t>108622</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Kennedy, Christian</t>
+          <t>Sasso, Daniel</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>Business Law</t>
+          <t>Digital Media</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -2560,12 +2560,12 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
@@ -2575,19 +2575,19 @@
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>431 Algebra II/Trig H</t>
+          <t>553 AP Chemistry</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>120546</t>
+          <t>108437</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Williams, Luke</t>
+          <t>Basich, Tomislav</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>Studio Art I</t>
+          <t>TV/Film Production &amp; Editing I</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
@@ -2628,24 +2628,24 @@
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>period_saturation</t>
+          <t>singleton_collision</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>443 AP Precalculus</t>
+          <t>830 Theology 11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>108592</t>
+          <t>107970</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>D'Silva, Ryan</t>
+          <t>Stokes, Devan</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -2691,19 +2691,19 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>443 AP Precalculus</t>
+          <t>430 Algebra II/Trig</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>108174</t>
+          <t>108070</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Barbara, Mario</t>
+          <t>Robins, Sean</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
@@ -2711,12 +2711,12 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>757</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Business Law</t>
+          <t>International Business Strategies</t>
         </is>
       </c>
       <c r="F39" s="4" t="n">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Full-Year</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
@@ -2749,19 +2749,19 @@
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>139 AP English Language</t>
+          <t>430 Algebra II/Trig</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>108077</t>
+          <t>108137</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Gentoso, Luca</t>
+          <t>Egbert, Gabriel</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>Business Law</t>
+          <t>TV/Film Production &amp; Editing I</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -2802,24 +2802,24 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>period_saturation</t>
+          <t>singleton_collision</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>733 AP U.S. History</t>
+          <t>310 Spanish I</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>107636</t>
+          <t>107801</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Durkin, Rowan</t>
+          <t>Scilletti, Anthony</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>727</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Programming</t>
+          <t>Sports and Entertainment Marketing</t>
         </is>
       </c>
       <c r="F41" s="4" t="n">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
@@ -2865,19 +2865,19 @@
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>830 Theology 11</t>
+          <t>332 Italian III</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>107648</t>
+          <t>107632</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Khym, Logan</t>
+          <t>Waldow, Aidan</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>757</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>Business Law</t>
+          <t>International Business Strategies</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
@@ -2908,12 +2908,12 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Full-Year</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -2923,19 +2923,19 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>131 British Literature H</t>
+          <t>530 Physics</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>107246</t>
+          <t>107623</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Gambardella, Thomas</t>
+          <t>Neyland, Johnny</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
@@ -2943,12 +2943,12 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>727</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Programming</t>
+          <t>Sports and Entertainment Marketing</t>
         </is>
       </c>
       <c r="F43" s="4" t="n">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
@@ -2981,19 +2981,19 @@
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>830 Theology 11</t>
+          <t>131 British Literature H</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>121441</t>
+          <t>107150</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Wyda, Andrew</t>
+          <t>Ferro, Preston</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>Sports and Entertainment Marketing</t>
+          <t>Studio Art I</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -3039,19 +3039,19 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>450 Calculus H</t>
+          <t>130 British Literature</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>116201</t>
+          <t>107177</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Best, Charles</t>
+          <t>Siracuse, David</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>473</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>International Business Strategies</t>
+          <t>Introduction to Programming</t>
         </is>
       </c>
       <c r="F45" s="4" t="n">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>Full-Year</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
@@ -3097,19 +3097,19 @@
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>631 CPR-AED Training/PE</t>
+          <t>830 Theology 11</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>108666</t>
+          <t>106794</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Foye, John</t>
+          <t>Campbell, Kevin</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
@@ -3117,12 +3117,12 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>757</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>Studio Art I</t>
+          <t>International Business Strategies</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Full-Year</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
@@ -3155,32 +3155,32 @@
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>531 Physics H</t>
+          <t>330 Spanish III</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>106206</t>
+          <t>119656</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>DiMaulo, William</t>
+          <t>Pierce, Dylan</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>727</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>Forensics</t>
+          <t>Sports and Entertainment Marketing</t>
         </is>
       </c>
       <c r="F47" s="4" t="n">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>Full-Year</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
@@ -3213,32 +3213,32 @@
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>543 Anatomy/Physiology H</t>
+          <t>723 Introduction to Political Science</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>106211</t>
+          <t>110098</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Ruggiero, Richard</t>
+          <t>Arment, Jayden</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>Digital Media</t>
+          <t>Studio Art I</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
@@ -3256,12 +3256,12 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
@@ -3271,32 +3271,32 @@
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>141 College English Honors</t>
+          <t>530 Physics</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>106224</t>
+          <t>107073</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Jensen, Hugh</t>
+          <t>Russo, Gavin</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>732</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>Digital Media</t>
+          <t>Business Law</t>
         </is>
       </c>
       <c r="F49" s="4" t="n">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
@@ -3329,32 +3329,32 @@
       </c>
       <c r="L49" s="5" t="inlineStr">
         <is>
-          <t>741 Psychology</t>
+          <t>631 CPR-AED Training/PE</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>106205</t>
+          <t>108738</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Dolan, Liam</t>
+          <t>Ramos, Kane</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>757</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
         <is>
-          <t>Introduction to Programming</t>
+          <t>International Business Strategies</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Full-Year</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
@@ -3387,32 +3387,32 @@
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>743 AP European History</t>
+          <t>531 Physics H</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>106174</t>
+          <t>108938</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>Adames, Alberto</t>
+          <t>Flett, James</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
         <is>
-          <t>Forensics</t>
+          <t>Studio Art I</t>
         </is>
       </c>
       <c r="F51" s="4" t="n">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>Full-Year</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
@@ -3445,32 +3445,32 @@
       </c>
       <c r="L51" s="5" t="inlineStr">
         <is>
-          <t>595 Engineering Design</t>
+          <t>443 AP Precalculus</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>106249</t>
+          <t>120546</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Larrondo, Gavin</t>
+          <t>Williams, Luke</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>Introduction to Programming</t>
+          <t>Studio Art I</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="K52" s="3" t="inlineStr">
@@ -3503,32 +3503,32 @@
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>141 College English Honors</t>
+          <t>139 AP English Language</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>106337</t>
+          <t>108077</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>Pocsi, Joseph</t>
+          <t>Gentoso, Luca</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>732</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>TV/Film Production II</t>
+          <t>Business Law</t>
         </is>
       </c>
       <c r="F53" s="4" t="n">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
@@ -3561,32 +3561,32 @@
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>756 Introduction to Law</t>
+          <t>440 Precalculus</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>106218</t>
+          <t>107246</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>Zervoudis, Stylianos</t>
+          <t>Gambardella, Thomas</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>241</t>
+          <t>473</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>Studio Art I</t>
+          <t>Introduction to Programming</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Fall</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
@@ -3619,32 +3619,32 @@
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>448 Pre-college Math</t>
+          <t>830 Theology 11</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>106239</t>
+          <t>108666</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>DeFilippo, Daniel</t>
+          <t>Foye, John</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>241</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Introduction to Programming</t>
+          <t>Studio Art I</t>
         </is>
       </c>
       <c r="F55" s="4" t="n">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Fall</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
@@ -3677,19 +3677,19 @@
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>752 Economics H</t>
+          <t>131 British Literature H</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>113957</t>
+          <t>106248</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Svec, Dylan</t>
+          <t>Strayton, Ryder</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>2054</t>
+          <t>546</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
         <is>
-          <t>Digital Media</t>
+          <t>Forensics</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -3720,27 +3720,1129 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>851 Spirituality of Vocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>106192</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>De Noyelles, Matthew</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L57" s="5" t="inlineStr">
+        <is>
+          <t>595 Engineering Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>112306</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Blatt, Jacob</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>595 Engineering Design</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>105477</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>Hinspeter, Jack</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Digital Media</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>Fall</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L59" s="5" t="inlineStr">
+        <is>
+          <t>242 Studio Art II</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>106206</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>DiMaulo, William</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>543 Anatomy/Physiology H</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>106199</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>Dos Santos, Antonio</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>Studio Art I</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>Fall</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>351 AP Spanish</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>106211</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Ruggiero, Richard</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Digital Media</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>Fall</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>440 Precalculus</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>106224</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>Jensen, Hugh</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>Digital Media</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>Fall</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L63" s="5" t="inlineStr">
+        <is>
+          <t>741 Psychology</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>106295</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>Field, Dylan</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>2044</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>TV/Film Production II</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>Spring</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>851 Spirituality of Vocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>106205</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>Dolan, Liam</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>Introduction to Programming</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
           <t>F</t>
         </is>
       </c>
-      <c r="J56" s="2" t="inlineStr">
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>Fall</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L65" s="5" t="inlineStr">
+        <is>
+          <t>743 AP European History</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>106174</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Adames, Alberto</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>141 College English Honors</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>106356</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>Licitra, Matthew</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L67" s="5" t="inlineStr">
+        <is>
+          <t>851 Spirituality of Vocation</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>106249</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Larrondo, Gavin</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Introduction to Programming</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
         <is>
           <t>Spring</t>
         </is>
       </c>
-      <c r="K56" s="3" t="inlineStr">
-        <is>
-          <t>period_saturation</t>
-        </is>
-      </c>
-      <c r="L56" s="3" t="inlineStr">
-        <is>
-          <t>546 Forensics</t>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>763 AP U.S. Government &amp; Politics</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>117239</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>Tristani, Antonio</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L69" s="5" t="inlineStr">
+        <is>
+          <t>440 Precalculus</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>106218</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Zervoudis, Stylianos</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Studio Art I</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Spring</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>448 Pre-college Math</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>106218</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>Zervoudis, Stylianos</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>Digital Media</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>Fall</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L71" s="5" t="inlineStr">
+        <is>
+          <t>242 Studio Art II</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>106325</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Matthews, Zy'on</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>546</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Forensics</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>Full-Year</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>642 Nutrition &amp; Fitness/PE</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>107254</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>Butler, Jayden</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>Digital Media</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>Fall</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L73" s="5" t="inlineStr">
+        <is>
+          <t>242 Studio Art II</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>106239</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>DeFilippo, Daniel</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Introduction to Programming</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Fall</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>141 College English Honors</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>113957</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Svec, Dylan</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>2054</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>Digital Media</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>flexible</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>Fall</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>period_saturation</t>
+        </is>
+      </c>
+      <c r="L75" s="5" t="inlineStr">
+        <is>
+          <t>440 Precalculus</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L56"/>
+  <autoFilter ref="A1:L75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3765,7 +4867,7 @@
         </is>
       </c>
       <c r="B1" s="6" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
@@ -3775,7 +4877,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>54</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
@@ -3805,7 +4907,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -3815,7 +4917,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
@@ -3835,7 +4937,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -3845,7 +4947,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
